--- a/config/generated/templates/SnapshotCapture.xlsx
+++ b/config/generated/templates/SnapshotCapture.xlsx
@@ -754,8 +754,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Hp, Atk, Def, Spd, CritRate, CritDamage, EffectHitRate, EffectResistance, BreakEffect, EnergyRegenerationRate, OutgoingHealing, IncomingHealing, ShieldStrength, Aggro, ToughnessDamage" promptTitle="StatKind enum" prompt="Select a value from the dropdown." sqref="G8:G1007">
       <formula1>"Hp,Atk,Def,Spd,CritRate,CritDamage,EffectHitRate,EffectResistance,BreakEffect,EnergyRegenerationRate,OutgoingHealing,IncomingHealing,ShieldStrength,Aggro,ToughnessDamage"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Energy, SkillPoints, Hp, CharacterResource" promptTitle="ResourceKind enum" prompt="Select a value from the dropdown." sqref="H8:H1007">
-      <formula1>"Energy,SkillPoints,Hp,CharacterResource"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Energy, SkillPoints, Hp, CharacterResource, TeamResource" promptTitle="ResourceKind enum" prompt="Select a value from the dropdown." sqref="H8:H1007">
+      <formula1>"Energy,SkillPoints,Hp,CharacterResource,TeamResource"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/generated/templates/SnapshotCapture.xlsx
+++ b/config/generated/templates/SnapshotCapture.xlsx
@@ -31,16 +31,16 @@
     <t>@key</t>
   </si>
   <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
   </si>
   <si>
     <t>@schema</t>
   </si>
   <si>
-    <t>40659fcfdc2de7dd</t>
+    <t>25ad3878c2c338ff</t>
   </si>
   <si>
     <t>#name</t>
@@ -106,7 +106,7 @@
     <t>optional&lt;ref&lt;ValueExpression.id&gt;&gt;</t>
   </si>
   <si>
-    <t>#scope</t>
+    <t>#groups</t>
   </si>
   <si>
     <t>#input</t>
